--- a/QCM4_2_PHY.xlsx
+++ b/QCM4_2_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE9088C4-3F73-4D76-B83E-DB6B14B3E746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A17B4F5F-088C-4B7E-91D1-8E43796BD90D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="112">
   <si>
     <t>Question</t>
   </si>
@@ -357,8 +357,10 @@
     <t>$v_0^2 = \frac{g.h}{2}$</t>
   </si>
   <si>
+    <t>PHY_QCM1_4_Q2.png</t>
+  </si>
+  <si>
     <t>Un ballon de basketball : Un ballon de basketball de masse $m$ se déplace le long d'une piste ABCDE. La piste comporte : 
-&lt;img src="/images/PHY_QCM1_4_Q2.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
 Donner l'expression du travail du poids dans chaque partie.</t>
   </si>
 </sst>
@@ -422,7 +424,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -484,11 +486,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFA6A6A6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFA6A6A6"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -519,6 +532,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1225,9 +1241,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>99</v>
@@ -1250,6 +1266,9 @@
       <c r="H16" s="9"/>
       <c r="I16" s="9" t="s">
         <v>67</v>
+      </c>
+      <c r="J16" s="11" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">

--- a/QCM4_2_PHY.xlsx
+++ b/QCM4_2_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A17B4F5F-088C-4B7E-91D1-8E43796BD90D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B649268-BD75-42B9-8C6E-BE67E9ECD84F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -72,9 +72,6 @@
     <t>Autre</t>
   </si>
   <si>
-    <t>Chute verticale : Un joueur lance une bille métallique verticalement vers le haut. Les frottements dus à l'air sont négligés. L'axe vertical (Oz) est dirigé vers le haut. La date $t = 0$ est l'instant où la bille quitte la main du joueur. L'altitude $z$ est alors égale à $0$ et la vitesse initiale $v_0 = 5\text{ m.s}^{-1}$. Données : Masse de la bille : $m = 20\text{ g}$. Champ de pesanteur : $g = 10\text{ m.s}^{-2}$.</t>
-  </si>
-  <si>
     <t>Mouvement uniforme</t>
   </si>
   <si>
@@ -120,9 +117,6 @@
     <t>nul</t>
   </si>
   <si>
-    <t>Différentes formes d'énergie. Données: Intensité de pesanteur $g=10\text{ N.kg}^{-1}$. Constante de Planck : $h=6,63 \cdot 10^{-34}\text{ J.s}$</t>
-  </si>
-  <si>
     <t>$5.10^4\text{ J}$</t>
   </si>
   <si>
@@ -171,9 +165,6 @@
     <t>$E=\nu.h$</t>
   </si>
   <si>
-    <t>Le mouvement</t>
-  </si>
-  <si>
     <t>$\vec{a} = \vec{0}$</t>
   </si>
   <si>
@@ -225,15 +216,9 @@
     <t>$W(P) = mgH$</t>
   </si>
   <si>
-    <t>$W(P) = mgAB\cos\alpha$</t>
-  </si>
-  <si>
     <t>$W(P) = -mgAB\sin\alpha$</t>
   </si>
   <si>
-    <t>$W(P) = -mgh$</t>
-  </si>
-  <si>
     <t>$W(P) = -mgH$</t>
   </si>
   <si>
@@ -360,8 +345,28 @@
     <t>PHY_QCM1_4_Q2.png</t>
   </si>
   <si>
-    <t>Un ballon de basketball : Un ballon de basketball de masse $m$ se déplace le long d'une piste ABCDE. La piste comporte : 
-Donner l'expression du travail du poids dans chaque partie.</t>
+    <t>&lt;center&gt;&lt;b&gt;Chute verticale : &lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+&lt;br&gt;Un joueur lance une bille métallique verticalement vers le haut. Les frottements dus à l'air sont négligés. L'axe vertical (Oz) est dirigé vers le haut. La date $t = 0$ est l'instant où la bille quitte la main du joueur. L'altitude $z$ est alors égale à $0$ et la vitesse initiale $v_0 = 5\text{ m.s}^{-1}$. 
+&lt;br&gt;Données : 
+Masse de la bille : $m = 20\text{ g}$. $\quad$ Champ de pesanteur : $g = 10\text{ m.s}^{-2}$.</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Différentes formes d'énergie. &lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+Données: Intensité de pesanteur $g=10\text{ N.kg}^{-1}$. Constante de Planck : $h=6,63 \cdot 10^{-34}\text{ J.s}$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Le mouvement&lt;/b&gt;&lt;/center&gt;</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Un ballon de basketball : &lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+&lt;br&gt;Un ballon de basketball de masse $m$ se déplace le long d'une piste ABCDE. La piste comporte (Figure suivante). 
+&lt;br&gt;Donner l'expression du travail du poids dans chaque partie.</t>
+  </si>
+  <si>
+    <t>$W(P) =- mgH$</t>
+  </si>
+  <si>
+    <t>$W(P) = - mgAB\cos\alpha$</t>
   </si>
 </sst>
 </file>
@@ -886,96 +891,96 @@
     </row>
     <row r="2" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="9" t="s">
+      <c r="E2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="F2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="G2" s="9" t="s">
         <v>18</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>19</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
       <c r="B3" s="6" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="F3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="G3" s="7" t="s">
         <v>22</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>23</v>
       </c>
       <c r="H3" s="7"/>
       <c r="I3" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="B4" s="8" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="F4" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="G4" s="9" t="s">
         <v>26</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>27</v>
       </c>
       <c r="H4" s="9"/>
       <c r="I4" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>29</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>30</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>12</v>
@@ -987,175 +992,175 @@
     </row>
     <row r="6" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="H6" s="7"/>
       <c r="I6" s="7" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="7" t="s">
+      <c r="F7" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="G7" s="7" t="s">
         <v>33</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>35</v>
       </c>
       <c r="H7" s="7"/>
       <c r="I7" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="B8" s="8" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="G8" s="9" t="s">
         <v>37</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>39</v>
       </c>
       <c r="H8" s="9"/>
       <c r="I8" s="9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="G9" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>43</v>
       </c>
       <c r="H9" s="7"/>
       <c r="I9" s="7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B10" s="8" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="G10" s="9" t="s">
         <v>45</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>47</v>
       </c>
       <c r="H10" s="9"/>
       <c r="I10" s="9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>48</v>
+        <v>108</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>13</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>14</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>13</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>14</v>
@@ -1167,228 +1172,228 @@
     <row r="13" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="8" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="H13" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="F13" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>56</v>
-      </c>
       <c r="I13" s="9" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="B14" s="6" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="G14" s="7" t="s">
         <v>57</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>60</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>14</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="B15" s="8" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="G15" s="9" t="s">
         <v>61</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>64</v>
       </c>
       <c r="H15" s="9"/>
       <c r="I15" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="F16" s="9" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>67</v>
-      </c>
       <c r="G16" s="9" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H16" s="9"/>
       <c r="I16" s="9" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B17" s="6" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="7" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B18" s="8" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E18" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18" s="9" t="s">
         <v>72</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>74</v>
       </c>
       <c r="H18" s="9"/>
       <c r="I18" s="9" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B19" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B20" s="8" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H20" s="9"/>
       <c r="I20" s="9" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B21" s="6" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H21" s="7"/>
       <c r="I21" s="7" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/QCM4_2_PHY.xlsx
+++ b/QCM4_2_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B649268-BD75-42B9-8C6E-BE67E9ECD84F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{034199E7-1DFB-435F-9B4F-27D9A7EB7350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="H16" s="9"/>
       <c r="I16" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J16" s="11" t="s">
         <v>105</v>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="H20" s="9"/>
       <c r="I20" s="9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="H21" s="7"/>
       <c r="I21" s="7" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
